--- a/output/pdf_financials_xlsx/DEAL.xlsx
+++ b/output/pdf_financials_xlsx/DEAL.xlsx
@@ -5629,52 +5629,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.638124</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.014404</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.424344</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.416687</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.827012</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.051237</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.665687</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.121019</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.160115</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.146848</v>
       </c>
     </row>
     <row r="93">
@@ -9350,7 +9350,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10476,7 +10480,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11338,7 +11346,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12576,7 +12588,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -14050,7 +14066,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -14966,7 +14986,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -16808,7 +16832,11 @@
           <t>Share-based payment reserve 638,124</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.638124</v>
       </c>

--- a/output/pdf_financials_xlsx/DEAL.xlsx
+++ b/output/pdf_financials_xlsx/DEAL.xlsx
@@ -1020,43 +1020,43 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000598</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001831</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00294</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.019605</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.045216</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.011419</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001893</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.012143</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.016277</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.015631</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.015144</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.014297</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.003258</v>
       </c>
     </row>
     <row r="13">
@@ -1963,43 +1963,43 @@
         <v>-0.106506</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.160824</v>
+        <v>-0.161422</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.220933</v>
+        <v>-0.222764</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.115683</v>
+        <v>-0.118623</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.84654</v>
+        <v>-0.8661450000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.235549</v>
+        <v>-2.280765</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.916693</v>
+        <v>-7.928112</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.258425</v>
+        <v>-2.260318</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.391317</v>
+        <v>-6.40346</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-14.843831</v>
+        <v>-14.860108</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-16.823347</v>
+        <v>-16.838978</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-16.511132</v>
+        <v>-16.526276</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-18.194507</v>
+        <v>-18.208804</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-10.252128</v>
+        <v>-10.255386</v>
       </c>
     </row>
     <row r="28">
@@ -2073,43 +2073,43 @@
         <v>-0.09478499999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.150989</v>
+        <v>-0.151587</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.192477</v>
+        <v>-0.194308</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.113446</v>
+        <v>-0.116386</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.844565</v>
+        <v>-0.86417</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.230739</v>
+        <v>-2.275955</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.912247</v>
+        <v>-7.923666</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.256409</v>
+        <v>-2.258302</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.790785</v>
+        <v>-4.802928</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-11.726602</v>
+        <v>-11.742879</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-13.483618</v>
+        <v>-13.499249</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-13.512283</v>
+        <v>-13.527427</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-14.021908</v>
+        <v>-14.036205</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-10.124638</v>
+        <v>-10.127896</v>
       </c>
     </row>
     <row r="30">
@@ -2130,13 +2130,13 @@
         <v>-608.3761232349166</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-964.046737326012</v>
+        <v>-967.8648959264463</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1187.030527289547</v>
+        <v>-1198.322540857231</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-2048.131431666366</v>
+        <v>-2101.209604621773</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-4856.929173289208</v>
+        <v>-4955.376777199591</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-7402.302388459056</v>
+        <v>-7412.985433487076</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-4442.712004567918</v>
+        <v>-4446.439189588297</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-7342.664287279672</v>
+        <v>-7352.856203625434</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-1407.850523886838</v>
+        <v>-1409.482586701053</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-919.0628774934975</v>
+        <v>-920.0929246155688</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-2319.280823050713</v>
+        <v>-2321.645605213537</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-26541.80779111833</v>
+        <v>-26550.34866041</v>
       </c>
     </row>
     <row r="31">
@@ -2303,52 +2303,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.370327</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.241841</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.158594</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.105508</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.247959</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.172656</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>5.824829</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.296236</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.26873</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.090292</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.781456</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.930003</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.206781</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.208448</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.378555</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.101756</v>
       </c>
     </row>
     <row r="35">
@@ -2413,52 +2413,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.370327</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.241841</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.158594</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.105508</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.247959</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.172656</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>5.824829</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.296236</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.26873</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.090292</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.781456</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.930003</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.206781</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.208448</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.378555</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.101756</v>
       </c>
     </row>
     <row r="37">
@@ -3073,52 +3073,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.370327</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.242341</v>
+        <v>0.0005</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.163594</v>
+        <v>0.005</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.105508</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.247959</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1729</v>
+        <v>0.000244</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.942061</v>
+        <v>0.117232</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.406792</v>
+        <v>0.110556</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.44874</v>
+        <v>0.18001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.163789</v>
+        <v>0.07349700000000001</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.386488</v>
+        <v>0.605032</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.263714</v>
+        <v>0.333711</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.457581</v>
+        <v>0.2508</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.35889</v>
+        <v>0.150442</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.472201</v>
+        <v>0.09364599999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.483475</v>
+        <v>0.381719</v>
       </c>
     </row>
     <row r="49">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -35194,7 +35194,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -40852,7 +40852,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -42124,7 +42124,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">

--- a/output/pdf_financials_xlsx/DEAL.xlsx
+++ b/output/pdf_financials_xlsx/DEAL.xlsx
@@ -2039,7 +2039,7 @@
         <v>0.002016</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.600532</v>
+        <v>1.325087</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>3.117229</v>
@@ -2094,7 +2094,7 @@
         <v>-2.258302</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.802928</v>
+        <v>-5.078373</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-11.742879</v>
@@ -6063,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>1.600532</v>
+        <v>1.325087</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>3.117229</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -39724,7 +39724,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">

--- a/output/pdf_financials_xlsx/DEAL.xlsx
+++ b/output/pdf_financials_xlsx/DEAL.xlsx
@@ -763,25 +763,25 @@
         <v>0.292708</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.994287</v>
+        <v>1.610443</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.770286</v>
+        <v>1.332528</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.167038</v>
+        <v>2.020331</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.012673</v>
+        <v>2.796991</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>3.198379</v>
+        <v>3.999913</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>5.03056</v>
+        <v>5.815063</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>4.681321</v>
+        <v>5.367122</v>
       </c>
     </row>
     <row r="8">
@@ -4036,25 +4036,25 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.9792459999999999</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>2.224893</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.386759</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>3.016399</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>3.525978</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>4.516306</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>5.124435</v>
       </c>
     </row>
     <row r="65">
@@ -4201,25 +4201,25 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.03767</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.044066</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.301978</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.249075</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.38729</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.6279670000000001</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.747983</v>
       </c>
     </row>
     <row r="68">
@@ -6094,16 +6094,16 @@
         <v>-0.015344</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.013986</v>
+        <v>0.011914</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.001111</v>
+        <v>0.004487</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.00033</v>
+        <v>0.000276</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.000916</v>
+        <v>0.0009</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>-0.005181</v>
@@ -6378,7 +6378,7 @@
         <v>-0.030112</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.023771</v>
+        <v>0.023755</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0.027874</v>
@@ -6622,13 +6622,13 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.553928</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>1.352254</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.286865</v>
       </c>
     </row>
     <row r="111">
@@ -8069,7 +8069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T398"/>
+  <dimension ref="A1:T401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17396,7 +17396,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -20722,7 +20726,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23006,7 +23014,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -29353,10 +29365,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I226" s="5" t="n">
+        <v>0.00033</v>
       </c>
       <c r="J226" s="5" t="n">
         <v>0.000916</v>
@@ -30915,10 +30925,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I243" s="5" t="n">
+        <v>-0.030388</v>
       </c>
       <c r="J243" s="5" t="n">
         <v>0.023099</v>
@@ -31542,7 +31550,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -31563,10 +31575,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I250" s="5" t="n">
+        <v>-5.4e-05</v>
       </c>
       <c r="J250" s="5" t="n">
         <v>-1.6e-05</v>
@@ -31742,10 +31752,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F252" s="5" t="n">
+        <v>-0.058671</v>
       </c>
       <c r="G252" s="5" t="n">
         <v>-0.106506</v>
@@ -31756,10 +31764,8 @@
       <c r="I252" s="5" t="n">
         <v>-0.220933</v>
       </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J252" s="5" t="n">
+        <v>-0.115683</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -32106,7 +32112,11 @@
           <t>(Increase) decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32482,7 +32492,11 @@
           <t>Decrease (increase) in GST/HST receivable</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -32778,10 +32792,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F263" s="5" t="n">
+        <v>-0.120132</v>
       </c>
       <c r="G263" s="5" t="n">
         <v>-0.083247</v>
@@ -32876,10 +32888,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F264" s="5" t="n">
+        <v>0.361973</v>
       </c>
       <c r="G264" s="5" t="n">
         <v>0.241841</v>
@@ -32974,10 +32984,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F265" s="5" t="n">
+        <v>0.241841</v>
       </c>
       <c r="G265" s="5" t="n">
         <v>0.158594</v>
@@ -33054,29 +33062,29 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Depletion</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E266" s="5" t="n">
-        <v>-0.06485100000000001</v>
+          <t>Depletion</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F266" s="5" t="n">
-        <v>-0.058671</v>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017301</v>
+      </c>
+      <c r="G266" s="5" t="n">
+        <v>0.011721</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -33157,7 +33165,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Increase in amounts receivable</t>
+          <t>Decrease (increase) in amounts receivable</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -33165,16 +33173,16 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E267" s="5" t="n">
-        <v>-0.002412</v>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F267" s="5" t="n">
         <v>-0.015344</v>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G267" s="5" t="n">
+        <v>0.011914</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -33267,10 +33275,8 @@
       <c r="F268" s="5" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G268" s="5" t="n">
+        <v>-0.0045</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -33346,27 +33352,29 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Expenditures on property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" s="5" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase (decrease) in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="n">
+        <v>-0.06308900000000001</v>
+      </c>
+      <c r="G269" s="5" t="n">
+        <v>0.003978</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -33442,26 +33450,24 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Issuance of common share</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.06485100000000001</v>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>-0.058671</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -33537,29 +33543,29 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Revenue 12</t>
+          <t>Increase in amounts receivable</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="n">
+        <v>-0.002412</v>
+      </c>
+      <c r="F271" s="5" t="n">
+        <v>-0.015344</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -33621,38 +33627,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S271" s="5" t="n">
-        <v>0.60458</v>
-      </c>
-      <c r="T271" s="5" t="n">
-        <v>0.038146</v>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenditures on property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" s="5" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -33699,20 +33703,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O272" s="5" t="n">
-        <v>0.642306</v>
-      </c>
-      <c r="P272" s="5" t="n">
-        <v>0.427125</v>
-      </c>
-      <c r="Q272" s="5" t="n">
-        <v>0.175499</v>
-      </c>
-      <c r="R272" s="5" t="n">
-        <v>0.09568500000000001</v>
-      </c>
-      <c r="S272" s="5" t="n">
-        <v>0.040218</v>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -33723,24 +33737,26 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bad debts</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issuance of common share</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>0.3</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -33787,8 +33803,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O273" s="5" t="n">
-        <v>0.011442</v>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -33805,11 +33823,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S273" s="5" t="n">
-        <v>0.0835</v>
-      </c>
-      <c r="T273" s="5" t="n">
-        <v>0.106583</v>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -33818,19 +33840,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Revenue 12</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -33878,26 +33896,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N274" s="5" t="n">
-        <v>0.941252</v>
-      </c>
-      <c r="O274" s="5" t="n">
-        <v>0.542972</v>
-      </c>
-      <c r="P274" s="5" t="n">
-        <v>0.754718</v>
-      </c>
-      <c r="Q274" s="5" t="n">
-        <v>1.544465</v>
-      </c>
-      <c r="R274" s="5" t="n">
-        <v>1.370201</v>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S274" s="5" t="n">
-        <v>1.229693</v>
+        <v>0.60458</v>
       </c>
       <c r="T274" s="5" t="n">
-        <v>1.312593</v>
+        <v>0.038146</v>
       </c>
     </row>
     <row r="275">
@@ -33913,10 +33941,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Data access fees</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -33962,26 +33994,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N275" s="5" t="n">
-        <v>0.15786</v>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O275" s="5" t="n">
-        <v>0.125072</v>
+        <v>0.642306</v>
       </c>
       <c r="P275" s="5" t="n">
-        <v>0.6330249999999999</v>
+        <v>0.427125</v>
       </c>
       <c r="Q275" s="5" t="n">
-        <v>0.897312</v>
+        <v>0.175499</v>
       </c>
       <c r="R275" s="5" t="n">
-        <v>1.16313</v>
+        <v>0.09568500000000001</v>
       </c>
       <c r="S275" s="5" t="n">
-        <v>1.681842</v>
-      </c>
-      <c r="T275" s="5" t="n">
-        <v>1.18304</v>
+        <v>0.040218</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -33997,14 +34033,10 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 4</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Bad debts</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -34055,10 +34087,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O276" s="5" t="n">
+        <v>0.011442</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -34076,10 +34106,10 @@
         </is>
       </c>
       <c r="S276" s="5" t="n">
-        <v>4.172599</v>
+        <v>0.0835</v>
       </c>
       <c r="T276" s="5" t="n">
-        <v>0.12749</v>
+        <v>0.106583</v>
       </c>
     </row>
     <row r="277">
@@ -34095,7 +34125,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Interest and bank charges 6, 7, 9</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -34148,36 +34178,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N277" s="5" t="n">
+        <v>0.941252</v>
+      </c>
+      <c r="O277" s="5" t="n">
+        <v>0.542972</v>
+      </c>
+      <c r="P277" s="5" t="n">
+        <v>0.754718</v>
+      </c>
+      <c r="Q277" s="5" t="n">
+        <v>1.544465</v>
+      </c>
+      <c r="R277" s="5" t="n">
+        <v>1.370201</v>
       </c>
       <c r="S277" s="5" t="n">
-        <v>3.768652</v>
+        <v>1.229693</v>
       </c>
       <c r="T277" s="5" t="n">
-        <v>3.357065</v>
+        <v>1.312593</v>
       </c>
     </row>
     <row r="278">
@@ -34193,7 +34213,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Management and directors fees 9</t>
+          <t>Data access fees</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -34242,36 +34262,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N278" s="5" t="n">
+        <v>0.15786</v>
+      </c>
+      <c r="O278" s="5" t="n">
+        <v>0.125072</v>
+      </c>
+      <c r="P278" s="5" t="n">
+        <v>0.6330249999999999</v>
+      </c>
+      <c r="Q278" s="5" t="n">
+        <v>0.897312</v>
+      </c>
+      <c r="R278" s="5" t="n">
+        <v>1.16313</v>
       </c>
       <c r="S278" s="5" t="n">
-        <v>0.784503</v>
+        <v>1.681842</v>
       </c>
       <c r="T278" s="5" t="n">
-        <v>0.685801</v>
+        <v>1.18304</v>
       </c>
     </row>
     <row r="279">
@@ -34287,12 +34297,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Other general and administrative expenses</t>
+          <t>Depreciation and amortization 4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -34340,26 +34350,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N279" s="5" t="n">
-        <v>0.039385</v>
-      </c>
-      <c r="O279" s="5" t="n">
-        <v>0.198303</v>
-      </c>
-      <c r="P279" s="5" t="n">
-        <v>0.844136</v>
-      </c>
-      <c r="Q279" s="5" t="n">
-        <v>0.869077</v>
-      </c>
-      <c r="R279" s="5" t="n">
-        <v>0.399764</v>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S279" s="5" t="n">
-        <v>0.251624</v>
+        <v>4.172599</v>
       </c>
       <c r="T279" s="5" t="n">
-        <v>0.151945</v>
+        <v>0.12749</v>
       </c>
     </row>
     <row r="280">
@@ -34375,12 +34395,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Interest and bank charges 6, 7, 9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -34428,26 +34448,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N280" s="5" t="n">
-        <v>0.193176</v>
-      </c>
-      <c r="O280" s="5" t="n">
-        <v>0.424338</v>
-      </c>
-      <c r="P280" s="5" t="n">
-        <v>0.688899</v>
-      </c>
-      <c r="Q280" s="5" t="n">
-        <v>0.400038</v>
-      </c>
-      <c r="R280" s="5" t="n">
-        <v>0.669</v>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S280" s="5" t="n">
-        <v>0.6342100000000001</v>
+        <v>3.768652</v>
       </c>
       <c r="T280" s="5" t="n">
-        <v>0.799534</v>
+        <v>3.357065</v>
       </c>
     </row>
     <row r="281">
@@ -34463,10 +34493,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Regulatory and shareholder services</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Management and directors fees 9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -34512,26 +34546,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N281" s="5" t="n">
-        <v>0.025336</v>
-      </c>
-      <c r="O281" s="5" t="n">
-        <v>0.040767</v>
-      </c>
-      <c r="P281" s="5" t="n">
-        <v>0.102044</v>
-      </c>
-      <c r="Q281" s="5" t="n">
-        <v>0.062555</v>
-      </c>
-      <c r="R281" s="5" t="n">
-        <v>0.029801</v>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S281" s="5" t="n">
-        <v>0.035251</v>
+        <v>0.784503</v>
       </c>
       <c r="T281" s="5" t="n">
-        <v>0.060286</v>
+        <v>0.685801</v>
       </c>
     </row>
     <row r="282">
@@ -34547,10 +34591,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Rent and utilities</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Other general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -34596,34 +34644,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N282" s="5" t="n">
+        <v>0.039385</v>
+      </c>
+      <c r="O282" s="5" t="n">
+        <v>0.198303</v>
+      </c>
+      <c r="P282" s="5" t="n">
+        <v>0.844136</v>
+      </c>
+      <c r="Q282" s="5" t="n">
+        <v>0.869077</v>
       </c>
       <c r="R282" s="5" t="n">
-        <v>0.201015</v>
+        <v>0.399764</v>
       </c>
       <c r="S282" s="5" t="n">
-        <v>0.1142</v>
+        <v>0.251624</v>
       </c>
       <c r="T282" s="5" t="n">
-        <v>0.034918</v>
+        <v>0.151945</v>
       </c>
     </row>
     <row r="283">
@@ -34639,10 +34679,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Sales commissions</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -34688,32 +34732,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N283" s="5" t="n">
+        <v>0.193176</v>
+      </c>
+      <c r="O283" s="5" t="n">
+        <v>0.424338</v>
+      </c>
+      <c r="P283" s="5" t="n">
+        <v>0.688899</v>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>0.212816</v>
+        <v>0.400038</v>
       </c>
       <c r="R283" s="5" t="n">
-        <v>0.314349</v>
+        <v>0.669</v>
       </c>
       <c r="S283" s="5" t="n">
-        <v>0.168853</v>
+        <v>0.6342100000000001</v>
       </c>
       <c r="T283" s="5" t="n">
-        <v>0.007721</v>
+        <v>0.799534</v>
       </c>
     </row>
     <row r="284">
@@ -34729,14 +34767,10 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Salaries and benefits 9</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Regulatory and shareholder services</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -34782,36 +34816,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N284" s="5" t="n">
+        <v>0.025336</v>
+      </c>
+      <c r="O284" s="5" t="n">
+        <v>0.040767</v>
+      </c>
+      <c r="P284" s="5" t="n">
+        <v>0.102044</v>
+      </c>
+      <c r="Q284" s="5" t="n">
+        <v>0.062555</v>
+      </c>
+      <c r="R284" s="5" t="n">
+        <v>0.029801</v>
       </c>
       <c r="S284" s="5" t="n">
-        <v>5.864217</v>
+        <v>0.035251</v>
       </c>
       <c r="T284" s="5" t="n">
-        <v>1.805302</v>
+        <v>0.060286</v>
       </c>
     </row>
     <row r="285">
@@ -34827,7 +34851,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Share-based compensation 9</t>
+          <t>Rent and utilities</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -34896,16 +34920,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R285" s="5" t="n">
+        <v>0.201015</v>
       </c>
       <c r="S285" s="5" t="n">
-        <v>0.039096</v>
+        <v>0.1142</v>
       </c>
       <c r="T285" s="5" t="n">
-        <v>0.000776</v>
+        <v>0.034918</v>
       </c>
     </row>
     <row r="286">
@@ -34921,14 +34943,10 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Sales commissions</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -34984,20 +35002,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P286" s="5" t="n">
-        <v>0.072507</v>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q286" s="5" t="n">
-        <v>0.098206</v>
+        <v>0.212816</v>
       </c>
       <c r="R286" s="5" t="n">
-        <v>0.084359</v>
+        <v>0.314349</v>
       </c>
       <c r="S286" s="5" t="n">
-        <v>0.032215</v>
+        <v>0.168853</v>
       </c>
       <c r="T286" s="5" t="n">
-        <v>0.011663</v>
+        <v>0.007721</v>
       </c>
     </row>
     <row r="287">
@@ -35013,12 +35033,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Salaries and benefits 9</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -35066,26 +35086,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N287" s="5" t="n">
-        <v>2.3085</v>
-      </c>
-      <c r="O287" s="5" t="n">
-        <v>6.35203</v>
-      </c>
-      <c r="P287" s="5" t="n">
-        <v>15.216453</v>
-      </c>
-      <c r="Q287" s="5" t="n">
-        <v>17.642739</v>
-      </c>
-      <c r="R287" s="5" t="n">
-        <v>18.670376</v>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S287" s="5" t="n">
-        <v>18.900673</v>
+        <v>5.864217</v>
       </c>
       <c r="T287" s="5" t="n">
-        <v>9.644717</v>
+        <v>1.805302</v>
       </c>
     </row>
     <row r="288">
@@ -35101,14 +35131,10 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Loss before other income (expenses)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -35154,26 +35180,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N288" s="5" t="n">
-        <v>-2.257711</v>
-      </c>
-      <c r="O288" s="5" t="n">
-        <v>-6.35203</v>
-      </c>
-      <c r="P288" s="5" t="n">
-        <v>-15.056748</v>
-      </c>
-      <c r="Q288" s="5" t="n">
-        <v>-16.684994</v>
-      </c>
-      <c r="R288" s="5" t="n">
-        <v>-17.200152</v>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S288" s="5" t="n">
-        <v>-18.296093</v>
+        <v>0.039096</v>
       </c>
       <c r="T288" s="5" t="n">
-        <v>-9.606571000000001</v>
+        <v>0.000776</v>
       </c>
     </row>
     <row r="289">
@@ -35184,17 +35220,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -35242,26 +35278,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N289" s="5" t="n">
-        <v>0.001893</v>
-      </c>
-      <c r="O289" s="5" t="n">
-        <v>0.012143</v>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P289" s="5" t="n">
-        <v>0.016277</v>
+        <v>0.072507</v>
       </c>
       <c r="Q289" s="5" t="n">
-        <v>0.015631</v>
+        <v>0.098206</v>
       </c>
       <c r="R289" s="5" t="n">
-        <v>0.015144</v>
+        <v>0.084359</v>
       </c>
       <c r="S289" s="5" t="n">
-        <v>0.014297</v>
+        <v>0.032215</v>
       </c>
       <c r="T289" s="5" t="n">
-        <v>0.003258</v>
+        <v>0.011663</v>
       </c>
     </row>
     <row r="290">
@@ -35272,17 +35312,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Operating expenses total</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -35330,32 +35370,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N290" s="5" t="n">
+        <v>2.3085</v>
+      </c>
+      <c r="O290" s="5" t="n">
+        <v>6.35203</v>
+      </c>
+      <c r="P290" s="5" t="n">
+        <v>15.216453</v>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>-0.153984</v>
+        <v>17.642739</v>
       </c>
       <c r="R290" s="5" t="n">
-        <v>-0.092775</v>
+        <v>18.670376</v>
       </c>
       <c r="S290" s="5" t="n">
-        <v>-0.245209</v>
+        <v>18.900673</v>
       </c>
       <c r="T290" s="5" t="n">
-        <v>0.116656</v>
+        <v>9.644717</v>
       </c>
     </row>
     <row r="291">
@@ -35366,15 +35400,19 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Write-off other assets 3</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
+          <t>Loss before other income (expenses)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -35420,38 +35458,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N291" s="5" t="n">
+        <v>-2.257711</v>
+      </c>
+      <c r="O291" s="5" t="n">
+        <v>-6.35203</v>
+      </c>
+      <c r="P291" s="5" t="n">
+        <v>-15.056748</v>
+      </c>
+      <c r="Q291" s="5" t="n">
+        <v>-16.684994</v>
+      </c>
+      <c r="R291" s="5" t="n">
+        <v>-17.200152</v>
+      </c>
+      <c r="S291" s="5" t="n">
+        <v>-18.296093</v>
       </c>
       <c r="T291" s="5" t="n">
-        <v>-0.373878</v>
+        <v>-9.606571000000001</v>
       </c>
     </row>
     <row r="292">
@@ -35467,10 +35493,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>(Loss) gain on debt settlement 5,8</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -35516,36 +35546,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N292" s="5" t="n">
+        <v>0.001893</v>
+      </c>
+      <c r="O292" s="5" t="n">
+        <v>0.012143</v>
+      </c>
+      <c r="P292" s="5" t="n">
+        <v>0.016277</v>
+      </c>
+      <c r="Q292" s="5" t="n">
+        <v>0.015631</v>
+      </c>
+      <c r="R292" s="5" t="n">
+        <v>0.015144</v>
       </c>
       <c r="S292" s="5" t="n">
-        <v>0.332498</v>
+        <v>0.014297</v>
       </c>
       <c r="T292" s="5" t="n">
-        <v>-0.391593</v>
+        <v>0.003258</v>
       </c>
     </row>
     <row r="293">
@@ -35561,12 +35581,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -35614,26 +35634,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N293" s="5" t="n">
-        <v>0.000714</v>
-      </c>
-      <c r="O293" s="5" t="n">
-        <v>0.039287</v>
-      </c>
-      <c r="P293" s="5" t="n">
-        <v>0.212917</v>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q293" s="5" t="n">
-        <v>0.138353</v>
+        <v>-0.153984</v>
       </c>
       <c r="R293" s="5" t="n">
-        <v>0.24282</v>
+        <v>-0.092775</v>
       </c>
       <c r="S293" s="5" t="n">
-        <v>0.101586</v>
+        <v>-0.245209</v>
       </c>
       <c r="T293" s="5" t="n">
-        <v>0.645557</v>
+        <v>0.116656</v>
       </c>
     </row>
     <row r="294">
@@ -35649,7 +35675,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Loss for the year before taxes</t>
+          <t>Write-off other assets 3</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -35713,17 +35739,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q294" s="5" t="n">
-        <v>-16.823347</v>
-      </c>
-      <c r="R294" s="5" t="n">
-        <v>-16.957332</v>
-      </c>
-      <c r="S294" s="5" t="n">
-        <v>-18.194507</v>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T294" s="5" t="n">
-        <v>-10.252128</v>
+        <v>-0.373878</v>
       </c>
     </row>
     <row r="295">
@@ -35739,7 +35771,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Income tax recovery 10</t>
+          <t>(Loss) gain on debt settlement 5,8</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -35813,15 +35845,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S295" s="5" t="n">
+        <v>0.332498</v>
+      </c>
+      <c r="T295" s="5" t="n">
+        <v>-0.391593</v>
       </c>
     </row>
     <row r="296">
@@ -35837,12 +35865,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Other income (expenses) total</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -35891,25 +35919,25 @@
         </is>
       </c>
       <c r="N296" s="5" t="n">
-        <v>-2.258425</v>
+        <v>0.000714</v>
       </c>
       <c r="O296" s="5" t="n">
-        <v>-6.391317</v>
+        <v>0.039287</v>
       </c>
       <c r="P296" s="5" t="n">
-        <v>-14.843831</v>
+        <v>0.212917</v>
       </c>
       <c r="Q296" s="5" t="n">
-        <v>-16.823347</v>
+        <v>0.138353</v>
       </c>
       <c r="R296" s="5" t="n">
-        <v>-16.511132</v>
+        <v>0.24282</v>
       </c>
       <c r="S296" s="5" t="n">
-        <v>-18.194507</v>
+        <v>0.101586</v>
       </c>
       <c r="T296" s="5" t="n">
-        <v>-10.252128</v>
+        <v>0.645557</v>
       </c>
     </row>
     <row r="297">
@@ -35920,12 +35948,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>subsequent year</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
+          <t>Loss for the year before taxes</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -35989,21 +36017,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q297" s="5" t="n">
+        <v>-16.823347</v>
+      </c>
+      <c r="R297" s="5" t="n">
+        <v>-16.957332</v>
       </c>
       <c r="S297" s="5" t="n">
-        <v>-0.022257</v>
+        <v>-18.194507</v>
       </c>
       <c r="T297" s="5" t="n">
-        <v>-0.009552</v>
+        <v>-10.252128</v>
       </c>
     </row>
     <row r="298">
@@ -36014,17 +36038,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>subsequent year</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Income tax recovery 10</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -36097,11 +36121,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S298" s="5" t="n">
-        <v>-18.216764</v>
-      </c>
-      <c r="T298" s="5" t="n">
-        <v>-10.26168</v>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -36112,17 +36140,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>subsequent year</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -36170,36 +36198,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N299" s="5" t="n">
+        <v>-2.258425</v>
+      </c>
+      <c r="O299" s="5" t="n">
+        <v>-6.391317</v>
+      </c>
+      <c r="P299" s="5" t="n">
+        <v>-14.843831</v>
+      </c>
+      <c r="Q299" s="5" t="n">
+        <v>-16.823347</v>
+      </c>
+      <c r="R299" s="5" t="n">
+        <v>-16.511132</v>
       </c>
       <c r="S299" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-18.194507</v>
       </c>
       <c r="T299" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-10.252128</v>
       </c>
     </row>
     <row r="300">
@@ -36210,12 +36228,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>subsequent year</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Foreign currency translation adjustment</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -36264,26 +36282,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N300" s="5" t="n">
-        <v>69.542224</v>
-      </c>
-      <c r="O300" s="5" t="n">
-        <v>130.362116</v>
-      </c>
-      <c r="P300" s="5" t="n">
-        <v>213.391696</v>
-      </c>
-      <c r="Q300" s="5" t="n">
-        <v>253.331449</v>
-      </c>
-      <c r="R300" s="5" t="n">
-        <v>254.268635</v>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S300" s="5" t="n">
-        <v>313.313085</v>
+        <v>-0.022257</v>
       </c>
       <c r="T300" s="5" t="n">
-        <v>430.197042</v>
+        <v>-0.009552</v>
       </c>
     </row>
     <row r="301">
@@ -36292,15 +36320,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>subsequent year</t>
+        </is>
+      </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Revenue 14</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -36358,22 +36390,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P301" s="5" t="n">
-        <v>0.159705</v>
-      </c>
-      <c r="Q301" s="5" t="n">
-        <v>0.957745</v>
-      </c>
-      <c r="R301" s="5" t="n">
-        <v>1.470224</v>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S301" s="5" t="n">
-        <v>0.60458</v>
-      </c>
-      <c r="T301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-18.216764</v>
+      </c>
+      <c r="T301" s="5" t="n">
+        <v>-10.26168</v>
       </c>
     </row>
     <row r="302">
@@ -36384,17 +36420,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>subsequent year</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 4, 5, 6</t>
+          <t>Basic and diluted loss per common share</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -36452,22 +36488,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P302" s="5" t="n">
-        <v>3.117229</v>
-      </c>
-      <c r="Q302" s="5" t="n">
-        <v>3.339729</v>
-      </c>
-      <c r="R302" s="5" t="n">
-        <v>2.998849</v>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S302" s="5" t="n">
-        <v>4.172599</v>
-      </c>
-      <c r="T302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="T302" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="303">
@@ -36478,19 +36518,15 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Interest and bank charges 6, 8, 9, 11</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -36536,36 +36572,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N303" s="5" t="n">
+        <v>69.542224</v>
+      </c>
+      <c r="O303" s="5" t="n">
+        <v>130.362116</v>
+      </c>
+      <c r="P303" s="5" t="n">
+        <v>213.391696</v>
+      </c>
+      <c r="Q303" s="5" t="n">
+        <v>253.331449</v>
       </c>
       <c r="R303" s="5" t="n">
-        <v>1.743819</v>
+        <v>254.268635</v>
       </c>
       <c r="S303" s="5" t="n">
-        <v>3.768652</v>
-      </c>
-      <c r="T303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>313.313085</v>
+      </c>
+      <c r="T303" s="5" t="n">
+        <v>430.197042</v>
       </c>
     </row>
     <row r="304">
@@ -36574,17 +36600,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Management and directors fees 11</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Revenue 14</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -36640,19 +36666,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P304" s="5" t="n">
+        <v>0.159705</v>
       </c>
       <c r="Q304" s="5" t="n">
-        <v>0.784318</v>
+        <v>0.957745</v>
       </c>
       <c r="R304" s="5" t="n">
-        <v>0.801534</v>
+        <v>1.470224</v>
       </c>
       <c r="S304" s="5" t="n">
-        <v>0.784503</v>
+        <v>0.60458</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -36673,12 +36697,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Salaries and benefits 11</t>
+          <t>Depreciation and amortization 4, 5, 6</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -36736,19 +36760,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P305" s="5" t="n">
+        <v>3.117229</v>
       </c>
       <c r="Q305" s="5" t="n">
-        <v>8.274272</v>
+        <v>3.339729</v>
       </c>
       <c r="R305" s="5" t="n">
-        <v>8.626554</v>
+        <v>2.998849</v>
       </c>
       <c r="S305" s="5" t="n">
-        <v>5.864217</v>
+        <v>4.172599</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -36769,10 +36791,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Share-based compensation 11</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Interest and bank charges 6, 8, 9, 11</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -36823,20 +36849,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O306" s="5" t="n">
-        <v>1.278659</v>
-      </c>
-      <c r="P306" s="5" t="n">
-        <v>1.219331</v>
-      </c>
-      <c r="Q306" s="5" t="n">
-        <v>0.6144500000000001</v>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R306" s="5" t="n">
-        <v>0.172316</v>
+        <v>1.743819</v>
       </c>
       <c r="S306" s="5" t="n">
-        <v>0.039096</v>
+        <v>3.768652</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -36852,15 +36884,19 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Gain on settlement of interest payable 10</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
+          <t>Management and directors fees 11</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -36921,16 +36957,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q307" s="5" t="n">
+        <v>0.784318</v>
       </c>
       <c r="R307" s="5" t="n">
-        <v>0.320451</v>
+        <v>0.801534</v>
       </c>
       <c r="S307" s="5" t="n">
-        <v>0.332498</v>
+        <v>0.784503</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -36946,15 +36980,19 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Deferred tax recovery 9, 12</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>Salaries and benefits 11</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -37015,18 +37053,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q308" s="5" t="n">
+        <v>8.274272</v>
       </c>
       <c r="R308" s="5" t="n">
-        <v>0.4462</v>
-      </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.626554</v>
+      </c>
+      <c r="S308" s="5" t="n">
+        <v>5.864217</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -37042,12 +37076,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>in subsequent periods</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
+          <t>Share-based compensation 11</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -37101,26 +37135,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O309" s="5" t="n">
+        <v>1.278659</v>
+      </c>
+      <c r="P309" s="5" t="n">
+        <v>1.219331</v>
+      </c>
+      <c r="Q309" s="5" t="n">
+        <v>0.6144500000000001</v>
       </c>
       <c r="R309" s="5" t="n">
-        <v>-0.01979</v>
+        <v>0.172316</v>
       </c>
       <c r="S309" s="5" t="n">
-        <v>-0.022257</v>
+        <v>0.039096</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -37136,19 +37164,15 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>in subsequent periods</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of interest payable 10</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -37215,10 +37239,10 @@
         </is>
       </c>
       <c r="R310" s="5" t="n">
-        <v>-16.530922</v>
+        <v>0.320451</v>
       </c>
       <c r="S310" s="5" t="n">
-        <v>-18.216764</v>
+        <v>0.332498</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -37234,19 +37258,15 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>in subsequent periods</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery 9, 12</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -37313,10 +37333,12 @@
         </is>
       </c>
       <c r="R311" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="S311" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.4462</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -37330,17 +37352,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>in subsequent periods</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Revenue 15</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -37401,16 +37423,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q312" s="5" t="n">
-        <v>0.957745</v>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R312" s="5" t="n">
-        <v>1.470224</v>
-      </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.01979</v>
+      </c>
+      <c r="S312" s="5" t="n">
+        <v>-0.022257</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -37426,17 +37448,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>in subsequent periods</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Interest and bank charges 6, 8, 9, 10, 11</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -37499,16 +37521,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q313" s="5" t="n">
-        <v>0.254695</v>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R313" s="5" t="n">
-        <v>1.743819</v>
-      </c>
-      <c r="S313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.530922</v>
+      </c>
+      <c r="S313" s="5" t="n">
+        <v>-18.216764</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -37524,17 +37546,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>in subsequent periods</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Basic and diluted loss per common share</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -37592,19 +37614,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P314" s="5" t="n">
-        <v>0.176759</v>
-      </c>
-      <c r="Q314" s="5" t="n">
-        <v>0.115307</v>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R314" s="5" t="n">
-        <v>0.201015</v>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="S314" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -37618,17 +37642,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+      <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 10</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Revenue 15</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -37689,13 +37713,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q315" s="5" t="n">
+        <v>0.957745</v>
       </c>
       <c r="R315" s="5" t="n">
-        <v>0.320451</v>
+        <v>1.470224</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -37716,15 +37738,19 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>Interest and bank charges 6, 8, 9, 10, 11</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -37786,10 +37812,10 @@
         </is>
       </c>
       <c r="Q316" s="5" t="n">
-        <v>0.001198</v>
+        <v>0.254695</v>
       </c>
       <c r="R316" s="5" t="n">
-        <v>-0.01979</v>
+        <v>1.743819</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -37810,17 +37836,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Comprehensive gain (loss) for the year</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -37878,16 +37904,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P317" s="5" t="n">
+        <v>0.176759</v>
       </c>
       <c r="Q317" s="5" t="n">
-        <v>-16.822149</v>
+        <v>0.115307</v>
       </c>
       <c r="R317" s="5" t="n">
-        <v>-16.530922</v>
+        <v>0.201015</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -37913,14 +37937,10 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 10</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -37981,11 +38001,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q318" s="5" t="n">
-        <v>-7e-08</v>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R318" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.320451</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -38006,19 +38028,15 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -38064,22 +38082,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N319" s="5" t="n">
-        <v>0.00706</v>
-      </c>
-      <c r="O319" s="5" t="n">
-        <v>0.131065</v>
-      </c>
-      <c r="P319" s="5" t="n">
-        <v>0.163054</v>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q319" s="5" t="n">
-        <v>0.254695</v>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001198</v>
+      </c>
+      <c r="R319" s="5" t="n">
+        <v>-0.01979</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -38100,15 +38122,19 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Management and directors fees 10</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>Comprehensive gain (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -38164,16 +38190,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P320" s="5" t="n">
-        <v>0.853293</v>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q320" s="5" t="n">
-        <v>0.784318</v>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.822149</v>
+      </c>
+      <c r="R320" s="5" t="n">
+        <v>-16.530922</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
@@ -38194,17 +38220,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Salaries and benefits 10</t>
+          <t>Basic and diluted loss per common share</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -38262,16 +38288,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P321" s="5" t="n">
-        <v>6.164333</v>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q321" s="5" t="n">
-        <v>8.274272</v>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-08</v>
+      </c>
+      <c r="R321" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -38297,10 +38323,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Share-based compensation 10</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -38346,21 +38376,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N322" s="5" t="n">
+        <v>0.00706</v>
+      </c>
+      <c r="O322" s="5" t="n">
+        <v>0.131065</v>
       </c>
       <c r="P322" s="5" t="n">
-        <v>1.219331</v>
+        <v>0.163054</v>
       </c>
       <c r="Q322" s="5" t="n">
-        <v>0.6144500000000001</v>
+        <v>0.254695</v>
       </c>
       <c r="R322" t="inlineStr">
         <is>
@@ -38386,17 +38412,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Management and directors fees 10</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -38444,17 +38470,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N323" s="5" t="n">
-        <v>0.007847</v>
-      </c>
-      <c r="O323" s="5" t="n">
-        <v>-0.060421</v>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P323" s="5" t="n">
-        <v>0.005609</v>
+        <v>0.853293</v>
       </c>
       <c r="Q323" s="5" t="n">
-        <v>-0.153984</v>
+        <v>0.784318</v>
       </c>
       <c r="R323" t="inlineStr">
         <is>
@@ -38480,15 +38510,19 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 8</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Salaries and benefits 10</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -38545,12 +38579,10 @@
         </is>
       </c>
       <c r="P324" s="5" t="n">
-        <v>0.191031</v>
-      </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.164333</v>
+      </c>
+      <c r="Q324" s="5" t="n">
+        <v>8.274272</v>
       </c>
       <c r="R324" t="inlineStr">
         <is>
@@ -38576,12 +38608,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
+          <t>Share-based compensation 10</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -38635,14 +38667,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O325" s="5" t="n">
-        <v>-0.09829599999999999</v>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P325" s="5" t="n">
-        <v>-0.030641</v>
+        <v>1.219331</v>
       </c>
       <c r="Q325" s="5" t="n">
-        <v>0.001198</v>
+        <v>0.6144500000000001</v>
       </c>
       <c r="R325" t="inlineStr">
         <is>
@@ -38668,17 +38702,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -38727,16 +38761,16 @@
         </is>
       </c>
       <c r="N326" s="5" t="n">
-        <v>-2.258425</v>
+        <v>0.007847</v>
       </c>
       <c r="O326" s="5" t="n">
-        <v>-6.489613</v>
+        <v>-0.060421</v>
       </c>
       <c r="P326" s="5" t="n">
-        <v>-14.874472</v>
+        <v>0.005609</v>
       </c>
       <c r="Q326" s="5" t="n">
-        <v>-16.822149</v>
+        <v>-0.153984</v>
       </c>
       <c r="R326" t="inlineStr">
         <is>
@@ -38762,19 +38796,15 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Foreign currency translation</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 8</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -38820,17 +38850,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N327" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="O327" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P327" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="Q327" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.191031</v>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R327" t="inlineStr">
         <is>
@@ -38854,17 +38890,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Foreign currency translation</t>
+        </is>
+      </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Revenue 16</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -38915,18 +38951,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O328" s="5" t="n">
+        <v>-0.09829599999999999</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.159705</v>
-      </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.030641</v>
+      </c>
+      <c r="Q328" s="5" t="n">
+        <v>0.001198</v>
       </c>
       <c r="R328" t="inlineStr">
         <is>
@@ -38952,17 +38984,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Foreign currency translation</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 5, 6, 7</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -39010,21 +39042,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N329" s="5" t="n">
+        <v>-2.258425</v>
       </c>
       <c r="O329" s="5" t="n">
-        <v>1.600532</v>
+        <v>-6.489613</v>
       </c>
       <c r="P329" s="5" t="n">
-        <v>3.117229</v>
-      </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-14.874472</v>
+      </c>
+      <c r="Q329" s="5" t="n">
+        <v>-16.822149</v>
       </c>
       <c r="R329" t="inlineStr">
         <is>
@@ -39050,15 +39078,19 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Foreign currency translation</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Management and directors fees 12</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>Basic and diluted loss per common share</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -39105,18 +39137,16 @@
         </is>
       </c>
       <c r="N330" s="5" t="n">
-        <v>0.616156</v>
+        <v>-3e-08</v>
       </c>
       <c r="O330" s="5" t="n">
-        <v>0.562242</v>
+        <v>-5e-08</v>
       </c>
       <c r="P330" s="5" t="n">
-        <v>0.853293</v>
-      </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-08</v>
+      </c>
+      <c r="Q330" s="5" t="n">
+        <v>-7e-08</v>
       </c>
       <c r="R330" t="inlineStr">
         <is>
@@ -39140,19 +39170,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Rent 7</t>
+          <t>Revenue 16</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -39200,14 +39226,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N331" s="5" t="n">
-        <v>0.045975</v>
-      </c>
-      <c r="O331" s="5" t="n">
-        <v>0.096249</v>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P331" s="5" t="n">
-        <v>0.176759</v>
+        <v>0.159705</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
@@ -39243,12 +39273,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Depreciation and amortization 5, 6, 7</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -39296,14 +39326,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N332" s="5" t="n">
-        <v>0.255088</v>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O332" s="5" t="n">
-        <v>0.704734</v>
+        <v>1.600532</v>
       </c>
       <c r="P332" s="5" t="n">
-        <v>6.164333</v>
+        <v>3.117229</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -39339,10 +39371,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Travel (recovery)</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Management and directors fees 12</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -39389,13 +39425,13 @@
         </is>
       </c>
       <c r="N333" s="5" t="n">
-        <v>0.032853</v>
+        <v>0.616156</v>
       </c>
       <c r="O333" s="5" t="n">
-        <v>-0.006651</v>
+        <v>0.562242</v>
       </c>
       <c r="P333" s="5" t="n">
-        <v>0.072507</v>
+        <v>0.853293</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -39426,15 +39462,19 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Government grant</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Rent 7</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -39480,18 +39520,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N334" s="5" t="n">
+        <v>0.045975</v>
       </c>
       <c r="O334" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.096249</v>
+      </c>
+      <c r="P334" s="5" t="n">
+        <v>0.176759</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -39522,15 +39558,19 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Loss on disposal of assets 5</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -39576,18 +39616,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N335" s="5" t="n">
+        <v>0.255088</v>
       </c>
       <c r="O335" s="5" t="n">
-        <v>-0.001009</v>
-      </c>
-      <c r="P335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.704734</v>
+      </c>
+      <c r="P335" s="5" t="n">
+        <v>6.164333</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -39616,17 +39652,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Travel (recovery)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -39673,17 +39709,13 @@
         </is>
       </c>
       <c r="N336" s="5" t="n">
-        <v>0.050789</v>
-      </c>
-      <c r="O336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032853</v>
+      </c>
+      <c r="O336" s="5" t="n">
+        <v>-0.006651</v>
+      </c>
+      <c r="P336" s="5" t="n">
+        <v>0.072507</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -39714,19 +39746,15 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets 6</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Government grant</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -39778,7 +39806,7 @@
         </is>
       </c>
       <c r="O337" s="5" t="n">
-        <v>1.325087</v>
+        <v>0.01</v>
       </c>
       <c r="P337" t="inlineStr">
         <is>
@@ -39814,19 +39842,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Depreciation 5,7</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Loss on disposal of assets 5</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -39872,11 +39896,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N338" s="5" t="n">
-        <v>0.002016</v>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O338" s="5" t="n">
-        <v>0.275445</v>
+        <v>-0.001009</v>
       </c>
       <c r="P338" t="inlineStr">
         <is>
@@ -39910,17 +39936,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Share-based compensation (recovery) 11</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -39967,10 +39993,12 @@
         </is>
       </c>
       <c r="N339" s="5" t="n">
-        <v>-0.007657</v>
-      </c>
-      <c r="O339" s="5" t="n">
-        <v>1.278659</v>
+        <v>0.050789</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
@@ -40006,15 +40034,19 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Loss on disposal of property and equipment 5</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>Amortization of intangible assets 6</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -40060,11 +40092,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N340" s="5" t="n">
-        <v>-0.010454</v>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O340" s="5" t="n">
-        <v>-0.001009</v>
+        <v>1.325087</v>
       </c>
       <c r="P340" t="inlineStr">
         <is>
@@ -40098,15 +40132,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Depreciation 5,7</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -40144,19 +40182,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L341" s="5" t="n">
-        <v>0.045929</v>
-      </c>
-      <c r="M341" s="5" t="n">
-        <v>0.106889</v>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N341" s="5" t="n">
-        <v>0.050789</v>
-      </c>
-      <c r="O341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002016</v>
+      </c>
+      <c r="O341" s="5" t="n">
+        <v>0.275445</v>
       </c>
       <c r="P341" t="inlineStr">
         <is>
@@ -40192,12 +40232,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Accounting and administration</t>
+          <t>Share-based compensation (recovery) 11</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -40241,16 +40281,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M342" s="5" t="n">
-        <v>0.04428</v>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N342" s="5" t="n">
-        <v>0.007747</v>
-      </c>
-      <c r="O342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007657</v>
+      </c>
+      <c r="O342" s="5" t="n">
+        <v>1.278659</v>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -40286,12 +40326,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>Loss on disposal of property and equipment 5</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -40320,25 +40360,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J343" s="5" t="n">
-        <v>0.0104</v>
-      </c>
-      <c r="K343" s="5" t="n">
-        <v>0.017632</v>
-      </c>
-      <c r="L343" s="5" t="n">
-        <v>0.02193</v>
-      </c>
-      <c r="M343" s="5" t="n">
-        <v>0.032299</v>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N343" s="5" t="n">
-        <v>0.0285</v>
-      </c>
-      <c r="O343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.010454</v>
+      </c>
+      <c r="O343" s="5" t="n">
+        <v>-0.001009</v>
       </c>
       <c r="P343" t="inlineStr">
         <is>
@@ -40372,17 +40418,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Data access fees</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -40419,13 +40465,13 @@
         </is>
       </c>
       <c r="L344" s="5" t="n">
-        <v>0.234526</v>
+        <v>0.045929</v>
       </c>
       <c r="M344" s="5" t="n">
-        <v>0.237143</v>
+        <v>0.106889</v>
       </c>
       <c r="N344" s="5" t="n">
-        <v>0.15786</v>
+        <v>0.050789</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -40471,14 +40517,10 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Depreciation 4</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Accounting and administration</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -40509,17 +40551,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K345" s="5" t="n">
-        <v>0.001975</v>
-      </c>
-      <c r="L345" s="5" t="n">
-        <v>0.00481</v>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M345" s="5" t="n">
-        <v>0.004446</v>
+        <v>0.04428</v>
       </c>
       <c r="N345" s="5" t="n">
-        <v>0.002016</v>
+        <v>0.007747</v>
       </c>
       <c r="O345" t="inlineStr">
         <is>
@@ -40565,7 +40611,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Directors’ fees 8(a)</t>
+          <t>Audit</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -40594,24 +40640,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J346" s="5" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="K346" s="5" t="n">
+        <v>0.017632</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>0.12155</v>
+        <v>0.02193</v>
       </c>
       <c r="M346" s="5" t="n">
-        <v>0.1032</v>
+        <v>0.032299</v>
       </c>
       <c r="N346" s="5" t="n">
-        <v>0.1008</v>
+        <v>0.0285</v>
       </c>
       <c r="O346" t="inlineStr">
         <is>
@@ -40657,14 +40699,10 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Intangible amortization 5</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Data access fees</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -40701,15 +40739,13 @@
         </is>
       </c>
       <c r="L347" s="5" t="n">
-        <v>0.048426</v>
+        <v>0.234526</v>
       </c>
       <c r="M347" s="5" t="n">
-        <v>0.436815</v>
-      </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.237143</v>
+      </c>
+      <c r="N347" s="5" t="n">
+        <v>0.15786</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -40755,12 +40791,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Depreciation 4</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -40788,20 +40824,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J348" s="5" t="n">
-        <v>0.00382</v>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>0.112564</v>
+        <v>0.001975</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>0.131944</v>
+        <v>0.00481</v>
       </c>
       <c r="M348" s="5" t="n">
-        <v>0.159673</v>
+        <v>0.004446</v>
       </c>
       <c r="N348" s="5" t="n">
-        <v>0.156929</v>
+        <v>0.002016</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -40847,14 +40885,10 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Loan Interest expense 13</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Directors’ fees 8(a)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -40890,18 +40924,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L349" s="5" t="n">
+        <v>0.12155</v>
+      </c>
+      <c r="M349" s="5" t="n">
+        <v>0.1032</v>
       </c>
       <c r="N349" s="5" t="n">
-        <v>0.00706</v>
+        <v>0.1008</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -40947,10 +40977,14 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Licenses</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Intangible amortization 5</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -40987,13 +41021,15 @@
         </is>
       </c>
       <c r="L350" s="5" t="n">
-        <v>0.043717</v>
+        <v>0.048426</v>
       </c>
       <c r="M350" s="5" t="n">
-        <v>0.013592</v>
-      </c>
-      <c r="N350" s="5" t="n">
-        <v>0.012599</v>
+        <v>0.436815</v>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
@@ -41039,10 +41075,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Management compensation 8(a)</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr"/>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -41068,24 +41108,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J351" s="5" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="K351" s="5" t="n">
+        <v>0.112564</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>0.37655</v>
+        <v>0.131944</v>
       </c>
       <c r="M351" s="5" t="n">
-        <v>0.497854</v>
+        <v>0.159673</v>
       </c>
       <c r="N351" s="5" t="n">
-        <v>0.515356</v>
+        <v>0.156929</v>
       </c>
       <c r="O351" t="inlineStr">
         <is>
@@ -41131,12 +41167,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Loan Interest expense 13</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -41174,14 +41210,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L352" s="5" t="n">
-        <v>0.050107</v>
-      </c>
-      <c r="M352" s="5" t="n">
-        <v>0.115826</v>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N352" s="5" t="n">
-        <v>0.026786</v>
+        <v>0.00706</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -41227,7 +41267,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Professional and technical support fees</t>
+          <t>Licenses</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -41261,17 +41301,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K353" s="5" t="n">
-        <v>0.097495</v>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L353" s="5" t="n">
-        <v>0.261043</v>
+        <v>0.043717</v>
       </c>
       <c r="M353" s="5" t="n">
-        <v>1.846746</v>
+        <v>0.013592</v>
       </c>
       <c r="N353" s="5" t="n">
-        <v>0.941252</v>
+        <v>0.012599</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -41317,7 +41359,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Regulatory</t>
+          <t>Management compensation 8(a)</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -41346,24 +41388,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J354" s="5" t="n">
-        <v>0.010843</v>
-      </c>
-      <c r="K354" s="5" t="n">
-        <v>0.027144</v>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L354" s="5" t="n">
+        <v>0.37655</v>
       </c>
       <c r="M354" s="5" t="n">
-        <v>0.002352</v>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.497854</v>
+      </c>
+      <c r="N354" s="5" t="n">
+        <v>0.515356</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -41409,7 +41451,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -41442,20 +41484,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J355" s="5" t="n">
-        <v>0.0132</v>
-      </c>
-      <c r="K355" s="5" t="n">
-        <v>0.044387</v>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L355" s="5" t="n">
-        <v>0.08933099999999999</v>
+        <v>0.050107</v>
       </c>
       <c r="M355" s="5" t="n">
-        <v>0.176882</v>
+        <v>0.115826</v>
       </c>
       <c r="N355" s="5" t="n">
-        <v>0.045975</v>
+        <v>0.026786</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -41501,14 +41547,10 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Professional and technical support fees</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -41540,16 +41582,16 @@
         </is>
       </c>
       <c r="K356" s="5" t="n">
-        <v>0.054719</v>
+        <v>0.097495</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>0.342826</v>
+        <v>0.261043</v>
       </c>
       <c r="M356" s="5" t="n">
-        <v>0.624838</v>
+        <v>1.846746</v>
       </c>
       <c r="N356" s="5" t="n">
-        <v>0.255088</v>
+        <v>0.941252</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -41595,7 +41637,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Regulatory</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -41624,24 +41666,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L357" s="5" t="n">
-        <v>0.37628</v>
+      <c r="J357" s="5" t="n">
+        <v>0.010843</v>
+      </c>
+      <c r="K357" s="5" t="n">
+        <v>0.027144</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M357" s="5" t="n">
-        <v>0.40994</v>
-      </c>
-      <c r="N357" s="5" t="n">
-        <v>-0.007657</v>
+        <v>0.002352</v>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -41687,10 +41729,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Shareholder costs</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -41717,19 +41763,19 @@
         </is>
       </c>
       <c r="J358" s="5" t="n">
-        <v>0.000744</v>
+        <v>0.0132</v>
       </c>
       <c r="K358" s="5" t="n">
-        <v>0.003851</v>
+        <v>0.044387</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>0.017538</v>
+        <v>0.08933099999999999</v>
       </c>
       <c r="M358" s="5" t="n">
-        <v>0.003902</v>
+        <v>0.176882</v>
       </c>
       <c r="N358" s="5" t="n">
-        <v>0.004443</v>
+        <v>0.045975</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -41775,7 +41821,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Salaries and benefits</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -41808,20 +41854,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J359" s="5" t="n">
-        <v>0.006527</v>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>0.011519</v>
+        <v>0.054719</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>0.006646</v>
+        <v>0.342826</v>
       </c>
       <c r="M359" s="5" t="n">
-        <v>0.026263</v>
+        <v>0.624838</v>
       </c>
       <c r="N359" s="5" t="n">
-        <v>0.020893</v>
+        <v>0.255088</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -41867,7 +41915,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Travel and related</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -41896,20 +41944,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J360" s="5" t="n">
-        <v>0.01063</v>
-      </c>
-      <c r="K360" s="5" t="n">
-        <v>0.099754</v>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L360" s="5" t="n">
-        <v>0.10501</v>
+        <v>0.37628</v>
       </c>
       <c r="M360" s="5" t="n">
-        <v>0.108023</v>
+        <v>0.40994</v>
       </c>
       <c r="N360" s="5" t="n">
-        <v>0.032853</v>
+        <v>-0.007657</v>
       </c>
       <c r="O360" t="inlineStr">
         <is>
@@ -41955,43 +42007,49 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E361" s="5" t="n">
-        <v>0.064579</v>
-      </c>
-      <c r="F361" s="5" t="n">
-        <v>0.09834</v>
-      </c>
-      <c r="G361" s="5" t="n">
-        <v>0.121936</v>
-      </c>
-      <c r="H361" s="5" t="n">
-        <v>0.177552</v>
-      </c>
-      <c r="I361" s="5" t="n">
-        <v>0.239628</v>
+          <t>Shareholder costs</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J361" s="5" t="n">
-        <v>0.111235</v>
+        <v>0.000744</v>
       </c>
       <c r="K361" s="5" t="n">
-        <v>0.853528</v>
+        <v>0.003851</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>2.321018</v>
+        <v>0.017538</v>
       </c>
       <c r="M361" s="5" t="n">
-        <v>4.844074</v>
+        <v>0.003902</v>
       </c>
       <c r="N361" s="5" t="n">
-        <v>2.3085</v>
+        <v>0.004443</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
@@ -42037,43 +42095,53 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>Transfer agent</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E362" s="5" t="n">
-        <v>-0.064579</v>
-      </c>
-      <c r="F362" s="5" t="n">
-        <v>-0.061234</v>
-      </c>
-      <c r="G362" s="5" t="n">
-        <v>-0.106356</v>
-      </c>
-      <c r="H362" s="5" t="n">
-        <v>-0.16189</v>
-      </c>
-      <c r="I362" s="5" t="n">
-        <v>-0.223413</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J362" s="5" t="n">
-        <v>-0.105696</v>
+        <v>0.006527</v>
       </c>
       <c r="K362" s="5" t="n">
-        <v>-0.853528</v>
+        <v>0.011519</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>-2.275089</v>
+        <v>0.006646</v>
       </c>
       <c r="M362" s="5" t="n">
-        <v>-4.737185</v>
+        <v>0.026263</v>
       </c>
       <c r="N362" s="5" t="n">
-        <v>-2.257711</v>
+        <v>0.020893</v>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -42114,19 +42182,15 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Travel and related</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -42142,26 +42206,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H363" s="5" t="n">
-        <v>0.000598</v>
-      </c>
-      <c r="I363" s="5" t="n">
-        <v>0.001831</v>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J363" s="5" t="n">
-        <v>0.00294</v>
+        <v>0.01063</v>
       </c>
       <c r="K363" s="5" t="n">
-        <v>0.019605</v>
+        <v>0.099754</v>
       </c>
       <c r="L363" s="5" t="n">
-        <v>0.045216</v>
+        <v>0.10501</v>
       </c>
       <c r="M363" s="5" t="n">
-        <v>0.011419</v>
+        <v>0.108023</v>
       </c>
       <c r="N363" s="5" t="n">
-        <v>0.001893</v>
+        <v>0.032853</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>
@@ -42202,62 +42270,48 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Loss on disposal of fixed assets</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="n">
+        <v>0.064579</v>
+      </c>
+      <c r="F364" s="5" t="n">
+        <v>0.09834</v>
+      </c>
+      <c r="G364" s="5" t="n">
+        <v>0.121936</v>
+      </c>
+      <c r="H364" s="5" t="n">
+        <v>0.177552</v>
+      </c>
+      <c r="I364" s="5" t="n">
+        <v>0.239628</v>
+      </c>
+      <c r="J364" s="5" t="n">
+        <v>0.111235</v>
+      </c>
+      <c r="K364" s="5" t="n">
+        <v>0.853528</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>2.321018</v>
+      </c>
+      <c r="M364" s="5" t="n">
+        <v>4.844074</v>
       </c>
       <c r="N364" s="5" t="n">
-        <v>-0.010454</v>
+        <v>2.3085</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -42298,52 +42352,48 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Foreign exchange (loss) gain</t>
+          <t>Loss before other items</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E365" s="5" t="n">
-        <v>-0.000272</v>
+        <v>-0.064579</v>
       </c>
       <c r="F365" s="5" t="n">
-        <v>6.3e-05</v>
+        <v>-0.061234</v>
       </c>
       <c r="G365" s="5" t="n">
-        <v>-0.00015</v>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.106356</v>
+      </c>
+      <c r="H365" s="5" t="n">
+        <v>-0.16189</v>
+      </c>
+      <c r="I365" s="5" t="n">
+        <v>-0.223413</v>
       </c>
       <c r="J365" s="5" t="n">
-        <v>0.001424</v>
+        <v>-0.105696</v>
       </c>
       <c r="K365" s="5" t="n">
-        <v>-0.012617</v>
+        <v>-0.853528</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>-0.005676</v>
+        <v>-2.275089</v>
       </c>
       <c r="M365" s="5" t="n">
-        <v>-0.076783</v>
+        <v>-4.737185</v>
       </c>
       <c r="N365" s="5" t="n">
-        <v>0.007847</v>
+        <v>-2.257711</v>
       </c>
       <c r="O365" t="inlineStr">
         <is>
@@ -42389,10 +42439,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Intangible impairment 5</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -42408,38 +42462,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H366" s="5" t="n">
+        <v>0.000598</v>
+      </c>
+      <c r="I366" s="5" t="n">
+        <v>0.001831</v>
+      </c>
+      <c r="J366" s="5" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="K366" s="5" t="n">
+        <v>0.019605</v>
+      </c>
+      <c r="L366" s="5" t="n">
+        <v>0.045216</v>
       </c>
       <c r="M366" s="5" t="n">
-        <v>-3.114144</v>
-      </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011419</v>
+      </c>
+      <c r="N366" s="5" t="n">
+        <v>0.001893</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
@@ -42485,39 +42527,57 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Loss on disposal of fixed assets</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
-      <c r="E367" s="5" t="n">
-        <v>-0.000272</v>
-      </c>
-      <c r="F367" s="5" t="n">
-        <v>0.002563</v>
-      </c>
-      <c r="G367" s="5" t="n">
-        <v>-0.00015</v>
-      </c>
-      <c r="H367" s="5" t="n">
-        <v>0.001066</v>
-      </c>
-      <c r="I367" s="5" t="n">
-        <v>0.00248</v>
-      </c>
-      <c r="J367" s="5" t="n">
-        <v>-0.009986999999999999</v>
-      </c>
-      <c r="K367" s="5" t="n">
-        <v>0.006988</v>
-      </c>
-      <c r="L367" s="5" t="n">
-        <v>0.03954</v>
-      </c>
-      <c r="M367" s="5" t="n">
-        <v>-3.179508</v>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N367" s="5" t="n">
-        <v>-0.000714</v>
+        <v>-0.010454</v>
       </c>
       <c r="O367" t="inlineStr">
         <is>
@@ -42563,47 +42623,47 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Foreign exchange (loss) gain</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E368" s="5" t="n">
-        <v>-0.06485100000000001</v>
+        <v>-0.000272</v>
       </c>
       <c r="F368" s="5" t="n">
-        <v>-0.058671</v>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.3e-05</v>
+      </c>
+      <c r="G368" s="5" t="n">
+        <v>-0.00015</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I368" s="5" t="n">
-        <v>-0.220933</v>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J368" s="5" t="n">
-        <v>-0.115683</v>
+        <v>0.001424</v>
       </c>
       <c r="K368" s="5" t="n">
-        <v>-0.84654</v>
+        <v>-0.012617</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>-2.235549</v>
+        <v>-0.005676</v>
       </c>
       <c r="M368" s="5" t="n">
-        <v>-7.916693</v>
+        <v>-0.076783</v>
       </c>
       <c r="N368" s="5" t="n">
-        <v>-2.258425</v>
+        <v>0.007847</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -42644,24 +42704,24 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E369" s="5" t="n">
-        <v>16.325701</v>
-      </c>
-      <c r="F369" s="5" t="n">
-        <v>19.520906</v>
+          <t>Intangible impairment 5</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -42678,20 +42738,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J369" s="5" t="n">
-        <v>12.260447</v>
-      </c>
-      <c r="K369" s="5" t="n">
-        <v>46.489779</v>
-      </c>
-      <c r="L369" s="5" t="n">
-        <v>47.426293</v>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M369" s="5" t="n">
-        <v>51.668379</v>
-      </c>
-      <c r="N369" s="5" t="n">
-        <v>69.542224</v>
+        <v>-3.114144</v>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O369" t="inlineStr">
         <is>
@@ -42732,58 +42800,44 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Accounting and administration 8(b)</t>
+          <t>Other items total</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E370" s="5" t="n">
+        <v>-0.000272</v>
+      </c>
+      <c r="F370" s="5" t="n">
+        <v>0.002563</v>
+      </c>
+      <c r="G370" s="5" t="n">
+        <v>-0.00015</v>
+      </c>
+      <c r="H370" s="5" t="n">
+        <v>0.001066</v>
+      </c>
+      <c r="I370" s="5" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="J370" s="5" t="n">
+        <v>-0.009986999999999999</v>
       </c>
       <c r="K370" s="5" t="n">
-        <v>0.059416</v>
+        <v>0.006988</v>
       </c>
       <c r="L370" s="5" t="n">
-        <v>0.07406500000000001</v>
+        <v>0.03954</v>
       </c>
       <c r="M370" s="5" t="n">
-        <v>0.04428</v>
-      </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.179508</v>
+      </c>
+      <c r="N370" s="5" t="n">
+        <v>-0.000714</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
@@ -42824,24 +42878,24 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Corporate development</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="n">
+        <v>-0.06485100000000001</v>
+      </c>
+      <c r="F371" s="5" t="n">
+        <v>-0.058671</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -42853,31 +42907,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I371" s="5" t="n">
+        <v>-0.220933</v>
+      </c>
+      <c r="J371" s="5" t="n">
+        <v>-0.115683</v>
       </c>
       <c r="K371" s="5" t="n">
-        <v>0.006955</v>
+        <v>-0.84654</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>0.008224</v>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.235549</v>
+      </c>
+      <c r="M371" s="5" t="n">
+        <v>-7.916693</v>
+      </c>
+      <c r="N371" s="5" t="n">
+        <v>-2.258425</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
@@ -42918,24 +42964,24 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Basic and diluted weighted average</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Investment conference</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="n">
+        <v>16.325701</v>
+      </c>
+      <c r="F372" s="5" t="n">
+        <v>19.520906</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -42952,26 +42998,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J372" s="5" t="n">
+        <v>12.260447</v>
       </c>
       <c r="K372" s="5" t="n">
-        <v>0.005559</v>
+        <v>46.489779</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>0.006495</v>
-      </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>47.426293</v>
+      </c>
+      <c r="M372" s="5" t="n">
+        <v>51.668379</v>
+      </c>
+      <c r="N372" s="5" t="n">
+        <v>69.542224</v>
       </c>
       <c r="O372" t="inlineStr">
         <is>
@@ -43017,7 +43057,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Management and director compensation 8(a)</t>
+          <t>Accounting and administration 8(b)</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -43052,15 +43092,13 @@
         </is>
       </c>
       <c r="K373" s="5" t="n">
-        <v>0.2355</v>
+        <v>0.059416</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>0.4981</v>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07406500000000001</v>
+      </c>
+      <c r="M373" s="5" t="n">
+        <v>0.04428</v>
       </c>
       <c r="N373" t="inlineStr">
         <is>
@@ -43111,14 +43149,10 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Corporate development</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -43144,14 +43178,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J374" s="5" t="n">
-        <v>0.003206</v>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K374" s="5" t="n">
-        <v>0.060178</v>
+        <v>0.006955</v>
       </c>
       <c r="L374" s="5" t="n">
-        <v>0.050107</v>
+        <v>0.008224</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
@@ -43207,7 +43243,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Sponsorship</t>
+          <t>Investment conference</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -43242,12 +43278,10 @@
         </is>
       </c>
       <c r="K375" s="5" t="n">
-        <v>0.003998</v>
-      </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005559</v>
+      </c>
+      <c r="L375" s="5" t="n">
+        <v>0.006495</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
@@ -43303,7 +43337,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Website design and maintenance</t>
+          <t>Management and director compensation 8(a)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -43338,12 +43372,10 @@
         </is>
       </c>
       <c r="K376" s="5" t="n">
-        <v>0.010882</v>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.2355</v>
+      </c>
+      <c r="L376" s="5" t="n">
+        <v>0.4981</v>
       </c>
       <c r="M376" t="inlineStr">
         <is>
@@ -43394,44 +43426,52 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Petroleum and natural gas sales</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F377" s="5" t="n">
-        <v>0.046011</v>
-      </c>
-      <c r="G377" s="5" t="n">
-        <v>0.018789</v>
-      </c>
-      <c r="H377" s="5" t="n">
-        <v>0.017519</v>
-      </c>
-      <c r="I377" s="5" t="n">
-        <v>0.018839</v>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J377" s="5" t="n">
-        <v>0.006338</v>
-      </c>
-      <c r="K377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003206</v>
+      </c>
+      <c r="K377" s="5" t="n">
+        <v>0.060178</v>
+      </c>
+      <c r="L377" s="5" t="n">
+        <v>0.050107</v>
       </c>
       <c r="M377" t="inlineStr">
         <is>
@@ -43482,12 +43522,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Royalties</t>
+          <t>Sponsorship</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -43496,25 +43536,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F378" s="5" t="n">
-        <v>-0.008905</v>
-      </c>
-      <c r="G378" s="5" t="n">
-        <v>-0.003209</v>
-      </c>
-      <c r="H378" s="5" t="n">
-        <v>-0.001857</v>
-      </c>
-      <c r="I378" s="5" t="n">
-        <v>-0.002624</v>
-      </c>
-      <c r="J378" s="5" t="n">
-        <v>-0.000799</v>
-      </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K378" s="5" t="n">
+        <v>0.003998</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -43570,43 +43618,47 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Revenue total</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Website design and maintenance</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F379" s="5" t="n">
-        <v>0.037106</v>
-      </c>
-      <c r="G379" s="5" t="n">
-        <v>0.01558</v>
-      </c>
-      <c r="H379" s="5" t="n">
-        <v>0.015662</v>
-      </c>
-      <c r="I379" s="5" t="n">
-        <v>0.016215</v>
-      </c>
-      <c r="J379" s="5" t="n">
-        <v>0.005539</v>
-      </c>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K379" s="5" t="n">
+        <v>0.010882</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -43662,12 +43714,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Accounting and administration 9(b)</t>
+          <t>Petroleum and natural gas sales</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -43676,31 +43728,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F380" s="5" t="n">
+        <v>0.046011</v>
+      </c>
+      <c r="G380" s="5" t="n">
+        <v>0.018789</v>
+      </c>
+      <c r="H380" s="5" t="n">
+        <v>0.017519</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>0.018839</v>
       </c>
       <c r="J380" s="5" t="n">
-        <v>0.01405</v>
-      </c>
-      <c r="K380" s="5" t="n">
-        <v>0.059416</v>
+        <v>0.006338</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -43756,12 +43802,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Accretion of decommissioning liabilities</t>
+          <t>Royalties</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -43771,23 +43817,19 @@
         </is>
       </c>
       <c r="F381" s="5" t="n">
-        <v>0.000171</v>
+        <v>-0.008905</v>
       </c>
       <c r="G381" s="5" t="n">
-        <v>0.000146</v>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003209</v>
+      </c>
+      <c r="H381" s="5" t="n">
+        <v>-0.001857</v>
+      </c>
+      <c r="I381" s="5" t="n">
+        <v>-0.002624</v>
       </c>
       <c r="J381" s="5" t="n">
-        <v>3.7e-05</v>
+        <v>-0.000799</v>
       </c>
       <c r="K381" t="inlineStr">
         <is>
@@ -43848,17 +43890,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Depletion and depreciation 4</t>
+          <t>Revenue total</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -43866,25 +43908,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F382" s="5" t="n">
+        <v>0.037106</v>
       </c>
       <c r="G382" s="5" t="n">
-        <v>0.011721</v>
+        <v>0.01558</v>
       </c>
       <c r="H382" s="5" t="n">
-        <v>0.009835</v>
+        <v>0.015662</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>0.028456</v>
+        <v>0.016215</v>
       </c>
       <c r="J382" s="5" t="n">
-        <v>0.002237</v>
-      </c>
-      <c r="K382" s="5" t="n">
-        <v>0.001975</v>
+        <v>0.005539</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -43945,7 +43987,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Management and director compensation 9(a)</t>
+          <t>Accounting and administration 9(b)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -43975,10 +44017,10 @@
         </is>
       </c>
       <c r="J383" s="5" t="n">
-        <v>0.024</v>
+        <v>0.01405</v>
       </c>
       <c r="K383" s="5" t="n">
-        <v>0.2355</v>
+        <v>0.059416</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -44039,7 +44081,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Petroleum operating costs</t>
+          <t>Accretion of decommissioning liabilities</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -44048,15 +44090,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F384" s="5" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="G384" s="5" t="n">
+        <v>0.000146</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
@@ -44069,7 +44107,7 @@
         </is>
       </c>
       <c r="J384" s="5" t="n">
-        <v>0.005827</v>
+        <v>3.7e-05</v>
       </c>
       <c r="K384" t="inlineStr">
         <is>
@@ -44135,12 +44173,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Depletion and depreciation 4</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -44153,26 +44191,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G385" s="5" t="n">
+        <v>0.011721</v>
+      </c>
+      <c r="H385" s="5" t="n">
+        <v>0.009835</v>
+      </c>
+      <c r="I385" s="5" t="n">
+        <v>0.028456</v>
       </c>
       <c r="J385" s="5" t="n">
-        <v>0.005714</v>
+        <v>0.002237</v>
       </c>
       <c r="K385" s="5" t="n">
-        <v>0.097495</v>
+        <v>0.001975</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -44228,12 +44260,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment 4</t>
+          <t>Management and director compensation 9(a)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -44263,12 +44295,10 @@
         </is>
       </c>
       <c r="J386" s="5" t="n">
-        <v>-0.014351</v>
-      </c>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024</v>
+      </c>
+      <c r="K386" s="5" t="n">
+        <v>0.2355</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -44329,7 +44359,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>Petroleum operating costs</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -44338,17 +44368,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F387" s="5" t="n">
-        <v>0.017901</v>
-      </c>
-      <c r="G387" s="5" t="n">
-        <v>0.012655</v>
-      </c>
-      <c r="H387" s="5" t="n">
-        <v>0.01022</v>
-      </c>
-      <c r="I387" s="5" t="n">
-        <v>0.008892000000000001</v>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J387" s="5" t="n">
         <v>0.005827</v>
@@ -44417,10 +44455,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Impairment of property, plant and equipment 4</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -44436,21 +44478,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H388" s="5" t="n">
-        <v>0.047493</v>
-      </c>
-      <c r="I388" s="5" t="n">
-        <v>0.117374</v>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J388" s="5" t="n">
+        <v>0.005714</v>
+      </c>
+      <c r="K388" s="5" t="n">
+        <v>0.097495</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -44506,36 +44548,42 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E389" s="5" t="n">
-        <v>0.064579</v>
-      </c>
-      <c r="F389" s="5" t="n">
-        <v>0.062967</v>
-      </c>
-      <c r="G389" s="5" t="n">
-        <v>0.097414</v>
-      </c>
-      <c r="H389" s="5" t="n">
-        <v>0.109817</v>
-      </c>
-      <c r="I389" s="5" t="n">
-        <v>0.08474</v>
+          <t>Loss on disposal of property, plant and equipment 4</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J389" s="5" t="n">
-        <v>0.103134</v>
+        <v>-0.014351</v>
       </c>
       <c r="K389" t="inlineStr">
         <is>
@@ -44601,7 +44649,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Accretion of decommissioning liabilities 5</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -44610,22 +44658,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F390" s="5" t="n">
+        <v>0.017901</v>
       </c>
       <c r="G390" s="5" t="n">
-        <v>0.000146</v>
+        <v>0.012655</v>
       </c>
       <c r="H390" s="5" t="n">
-        <v>0.000187</v>
+        <v>0.01022</v>
       </c>
       <c r="I390" s="5" t="n">
-        <v>0.000166</v>
+        <v>0.008892000000000001</v>
       </c>
       <c r="J390" s="5" t="n">
-        <v>3.7e-05</v>
+        <v>0.005827</v>
       </c>
       <c r="K390" t="inlineStr">
         <is>
@@ -44686,19 +44732,15 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Impairment of property, plant and equipment 4</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -44715,13 +44757,15 @@
         </is>
       </c>
       <c r="H391" s="5" t="n">
-        <v>0.000468</v>
+        <v>0.047493</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>0.0006489999999999999</v>
-      </c>
-      <c r="J391" s="5" t="n">
-        <v>0.001424</v>
+        <v>0.117374</v>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
@@ -44782,38 +44826,36 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Basic and diluted weighted average number of common shares outstanding</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="n">
+        <v>0.064579</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>19.520906</v>
+        <v>0.062967</v>
       </c>
       <c r="G392" s="5" t="n">
-        <v>19.520906</v>
+        <v>0.097414</v>
       </c>
       <c r="H392" s="5" t="n">
-        <v>19.520906</v>
+        <v>0.109817</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>11.109762</v>
+        <v>0.08474</v>
       </c>
       <c r="J392" s="5" t="n">
-        <v>12.260447</v>
+        <v>0.103134</v>
       </c>
       <c r="K392" t="inlineStr">
         <is>
@@ -44874,40 +44916,36 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Accretion of decommissioning liabilities 5</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F393" s="5" t="n">
-        <v>-0.058671</v>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G393" s="5" t="n">
-        <v>-0.106506</v>
+        <v>0.000146</v>
       </c>
       <c r="H393" s="5" t="n">
-        <v>-0.160824</v>
+        <v>0.000187</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>-0.220933</v>
-      </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000166</v>
+      </c>
+      <c r="J393" s="5" t="n">
+        <v>3.7e-05</v>
       </c>
       <c r="K393" t="inlineStr">
         <is>
@@ -44973,7 +45011,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Foreign exchange gain</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -44991,21 +45029,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G394" s="5" t="n">
-        <v>-0.00015</v>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H394" s="5" t="n">
         <v>0.000468</v>
       </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I394" s="5" t="n">
+        <v>0.0006489999999999999</v>
+      </c>
+      <c r="J394" s="5" t="n">
+        <v>0.001424</v>
       </c>
       <c r="K394" t="inlineStr">
         <is>
@@ -45066,17 +45102,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Depletion 5</t>
+          <t>Basic and diluted weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Depletion</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -45085,25 +45121,19 @@
         </is>
       </c>
       <c r="F395" s="5" t="n">
-        <v>0.017301</v>
+        <v>19.520906</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>0.011721</v>
-      </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>19.520906</v>
+      </c>
+      <c r="H395" s="5" t="n">
+        <v>19.520906</v>
+      </c>
+      <c r="I395" s="5" t="n">
+        <v>11.109762</v>
+      </c>
+      <c r="J395" s="5" t="n">
+        <v>12.260447</v>
       </c>
       <c r="K395" t="inlineStr">
         <is>
@@ -45169,12 +45199,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -45183,22 +45213,16 @@
         </is>
       </c>
       <c r="F396" s="5" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.058671</v>
+      </c>
+      <c r="G396" s="5" t="n">
+        <v>-0.106506</v>
+      </c>
+      <c r="H396" s="5" t="n">
+        <v>-0.160824</v>
+      </c>
+      <c r="I396" s="5" t="n">
+        <v>-0.220933</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -45264,17 +45288,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Depletion and depreciation 5</t>
+          <t>Foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -45282,18 +45306,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F397" s="5" t="n">
-        <v>0.017301</v>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G397" s="5" t="n">
+        <v>-0.00015</v>
+      </c>
+      <c r="H397" s="5" t="n">
+        <v>0.000468</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -45369,84 +45391,382 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
+          <t>Depletion 5</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Depletion</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F398" s="5" t="n">
+        <v>0.017301</v>
+      </c>
+      <c r="G398" s="5" t="n">
+        <v>0.011721</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F399" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Depletion and depreciation 5</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F400" s="5" t="n">
+        <v>0.017301</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
           <t>Accretion of decommissioning liabilities 6</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F398" s="5" t="n">
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F401" s="5" t="n">
         <v>0.000171</v>
       </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T398" t="inlineStr">
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
         <is>
           <t>-</t>
         </is>
